--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0CB7A6-F38C-A44F-831F-ED39B8DD71F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58728A43-DE24-FA48-8FFF-B502DD9834D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>c</t>
   </si>
@@ -70,6 +70,42 @@
   </si>
   <si>
     <t>b9</t>
+  </si>
+  <si>
+    <t>b10</t>
+  </si>
+  <si>
+    <t>b11</t>
+  </si>
+  <si>
+    <t>b01</t>
+  </si>
+  <si>
+    <t>b02</t>
+  </si>
+  <si>
+    <t>b03</t>
+  </si>
+  <si>
+    <t>b04</t>
+  </si>
+  <si>
+    <t>b05</t>
+  </si>
+  <si>
+    <t>b06</t>
+  </si>
+  <si>
+    <t>b07</t>
+  </si>
+  <si>
+    <t>b08</t>
+  </si>
+  <si>
+    <t>b09</t>
+  </si>
+  <si>
+    <t>b12</t>
   </si>
 </sst>
 </file>
@@ -447,45 +483,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA0ED39-87D3-8343-A519-7A0A4077056A}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="17" max="19" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -517,7 +562,7 @@
         <v>5.9537418076512728E-7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -545,8 +590,17 @@
       <c r="J3">
         <v>7.5910208047553726E-4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <v>2.6009999999999998E-4</v>
+      </c>
+      <c r="L3">
+        <v>7.9499999999999994E-5</v>
+      </c>
+      <c r="M3">
+        <v>3.0700000000000001E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -571,8 +625,17 @@
       <c r="J4">
         <v>3.6020137936290199E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <v>1.8501199999999999E-2</v>
+      </c>
+      <c r="L4">
+        <v>9.4885999999999998E-3</v>
+      </c>
+      <c r="M4">
+        <v>4.7800999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -594,8 +657,17 @@
       <c r="J5">
         <v>0.27756344307270231</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <v>0.2029175</v>
+      </c>
+      <c r="L5">
+        <v>0.14469409999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.10114480000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -614,8 +686,17 @@
       <c r="J6">
         <v>0.49661351165980794</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6">
+        <v>0.5064902</v>
+      </c>
+      <c r="L6">
+        <v>0.48977730000000003</v>
+      </c>
+      <c r="M6">
+        <v>0.4562812</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -630,6 +711,15 @@
       </c>
       <c r="J7">
         <v>0.18904320987654322</v>
+      </c>
+      <c r="K7">
+        <v>0.27183099999999999</v>
+      </c>
+      <c r="L7">
+        <v>0.35596050000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.43776320000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58728A43-DE24-FA48-8FFF-B502DD9834D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E1708-BE5D-8748-9AC8-D6B27AD12815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295E1708-BE5D-8748-9AC8-D6B27AD12815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6376F6E2-B586-8E4B-8884-5D6459703C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>
@@ -561,6 +561,15 @@
       <c r="J2">
         <v>5.9537418076512728E-7</v>
       </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6376F6E2-B586-8E4B-8884-5D6459703C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1A9F54-F94A-5543-8193-85276A877616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58728A43-DE24-FA48-8FFF-B502DD9834D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5948A6-3ED6-A344-85A7-C569BE83B170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>c</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>b12</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -483,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA0ED39-87D3-8343-A519-7A0A4077056A}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="17" max="19" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -720,6 +726,58 @@
       </c>
       <c r="M7">
         <v>0.43776320000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="7:14" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22">
+        <v>1.993312757201646E-2</v>
+      </c>
+      <c r="I22">
+        <v>6.7515432098765428E-3</v>
+      </c>
+      <c r="J22">
+        <v>2.2683756287151351E-3</v>
+      </c>
+      <c r="K22">
+        <v>7.5910208047553726E-4</v>
+      </c>
+      <c r="L22">
+        <v>2.6009999999999998E-4</v>
+      </c>
+      <c r="M22">
+        <v>7.9499999999999994E-5</v>
+      </c>
+      <c r="N22">
+        <v>3.0700000000000001E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="7:14" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>7</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>11</v>
+      </c>
+      <c r="N23">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1A9F54-F94A-5543-8193-85276A877616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBB1F7F-07F9-4A43-BA95-EC848BDE57BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
+    <workbookView xWindow="37000" yWindow="6960" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>
   <sheets>
     <sheet name="percent" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>c</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>b12</t>
+  </si>
+  <si>
+    <t>b13</t>
+  </si>
+  <si>
+    <t>b14</t>
+  </si>
+  <si>
+    <t>b15</t>
   </si>
 </sst>
 </file>
@@ -483,13 +492,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA0ED39-87D3-8343-A519-7A0A4077056A}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="17" max="19" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,8 +538,17 @@
       <c r="M1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -570,8 +588,17 @@
       <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -608,8 +635,17 @@
       <c r="M3">
         <v>3.0700000000000001E-5</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -643,8 +679,17 @@
       <c r="M4">
         <v>4.7800999999999998E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N4">
+        <v>2.1362305E-3</v>
+      </c>
+      <c r="O4">
+        <v>1.0681152E-3</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -675,8 +720,17 @@
       <c r="M5">
         <v>0.10114480000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5">
+        <v>8.5111980000000004E-2</v>
+      </c>
+      <c r="O5">
+        <v>6.4744679999999999E-2</v>
+      </c>
+      <c r="P5">
+        <v>4.9251280000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -704,8 +758,17 @@
       <c r="M6">
         <v>0.4562812</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6">
+        <v>0.3540295</v>
+      </c>
+      <c r="O6">
+        <v>0.26153379999999998</v>
+      </c>
+      <c r="P6">
+        <v>0.1771028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -730,8 +793,18 @@
       <c r="M7">
         <v>0.43776320000000002</v>
       </c>
+      <c r="N7">
+        <v>0.54496</v>
+      </c>
+      <c r="O7">
+        <v>0.65505999999999998</v>
+      </c>
+      <c r="P7">
+        <v>0.77354000000000001</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data/grid_table.xlsx
+++ b/data/grid_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/biodatascience/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBB1F7F-07F9-4A43-BA95-EC848BDE57BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639A3D2D-1AF0-244D-A693-2CCBBF1FE25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37000" yWindow="6960" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
+    <workbookView xWindow="10080" yWindow="2440" windowWidth="28240" windowHeight="17240" xr2:uid="{FB36625E-1E1B-1540-816B-A9138A8171B4}"/>
   </bookViews>
   <sheets>
     <sheet name="percent" sheetId="2" r:id="rId1"/>
@@ -156,8 +156,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -573,8 +574,8 @@
       <c r="H2">
         <v>2.143347050754458E-5</v>
       </c>
-      <c r="I2">
-        <v>3.5722450845907635E-6</v>
+      <c r="I2" s="1">
+        <v>3.5722450845907601E-6</v>
       </c>
       <c r="J2">
         <v>5.9537418076512728E-7</v>
@@ -686,7 +687,7 @@
         <v>1.0681152E-3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.3405759999999999E-4</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -804,7 +805,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
